--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.72998841117571</v>
+        <v>5.481123116816053</v>
       </c>
       <c r="D2" t="n">
-        <v>29.76394876694973</v>
+        <v>4.836641674629331</v>
       </c>
       <c r="E2" t="n">
-        <v>8.455927071391809</v>
+        <v>1.374088149101169</v>
       </c>
       <c r="F2" t="n">
-        <v>10.09461135701721</v>
+        <v>1.640374345515297</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.16585920169796</v>
+        <v>6.039452120275919</v>
       </c>
       <c r="D3" t="n">
-        <v>28.79145684970359</v>
+        <v>4.678611738076834</v>
       </c>
       <c r="E3" t="n">
-        <v>8.455927071391809</v>
+        <v>1.374088149101169</v>
       </c>
       <c r="F3" t="n">
-        <v>10.09461135701721</v>
+        <v>1.640374345515297</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.46446894075586</v>
+        <v>2.675476202872827</v>
       </c>
       <c r="D4" t="n">
-        <v>4.343915163543185</v>
+        <v>0.7058862140757676</v>
       </c>
       <c r="E4" t="n">
-        <v>8.455927071391809</v>
+        <v>1.374088149101169</v>
       </c>
       <c r="F4" t="n">
-        <v>10.09461135701721</v>
+        <v>1.640374345515297</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.08361362577615</v>
+        <v>4.888587214188624</v>
       </c>
       <c r="D5" t="n">
-        <v>30.68244555549775</v>
+        <v>4.985897402768384</v>
       </c>
       <c r="E5" t="n">
-        <v>8.455927071391809</v>
+        <v>1.374088149101169</v>
       </c>
       <c r="F5" t="n">
-        <v>10.09461135701721</v>
+        <v>1.640374345515297</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.93988837248279</v>
+        <v>3.240231860528454</v>
       </c>
       <c r="D6" t="n">
-        <v>20.89007805407233</v>
+        <v>3.394637683786754</v>
       </c>
       <c r="E6" t="n">
-        <v>8.455927071391809</v>
+        <v>1.374088149101169</v>
       </c>
       <c r="F6" t="n">
-        <v>10.09461135701721</v>
+        <v>1.640374345515297</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.37515284138142</v>
+        <v>3.310962336724481</v>
       </c>
       <c r="D7" t="n">
-        <v>22.04528600519983</v>
+        <v>3.582358975844973</v>
       </c>
       <c r="E7" t="n">
-        <v>8.455927071391809</v>
+        <v>1.374088149101169</v>
       </c>
       <c r="F7" t="n">
-        <v>10.09461135701721</v>
+        <v>1.640374345515297</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.90703051003729</v>
+        <v>5.34739245788106</v>
       </c>
       <c r="D8" t="n">
-        <v>33.61029594232799</v>
+        <v>5.461673090628299</v>
       </c>
       <c r="E8" t="n">
-        <v>8.455927071391809</v>
+        <v>1.374088149101169</v>
       </c>
       <c r="F8" t="n">
-        <v>10.09461135701721</v>
+        <v>1.640374345515297</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.0235883865217</v>
+        <v>4.553833112809776</v>
       </c>
       <c r="D9" t="n">
-        <v>26.51610939185078</v>
+        <v>4.308867776175751</v>
       </c>
       <c r="E9" t="n">
-        <v>8.455927071391809</v>
+        <v>1.374088149101169</v>
       </c>
       <c r="F9" t="n">
-        <v>10.09461135701721</v>
+        <v>1.640374345515297</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>46.02795741390377</v>
+        <v>7.479543079759363</v>
       </c>
       <c r="D10" t="n">
-        <v>46.35507508391312</v>
+        <v>7.532699701135883</v>
       </c>
       <c r="E10" t="n">
-        <v>8.455927071391809</v>
+        <v>1.374088149101169</v>
       </c>
       <c r="F10" t="n">
-        <v>10.09461135701721</v>
+        <v>1.640374345515297</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.71499909139698</v>
+        <v>4.341187352352009</v>
       </c>
       <c r="D11" t="n">
-        <v>26.0138110145992</v>
+        <v>4.227244289872369</v>
       </c>
       <c r="E11" t="n">
-        <v>8.455927071391809</v>
+        <v>1.374088149101169</v>
       </c>
       <c r="F11" t="n">
-        <v>10.09461135701721</v>
+        <v>1.640374345515297</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
